--- a/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
+++ b/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H312"/>
+  <dimension ref="A1:H377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8353,18 +8353,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -8374,7 +8378,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -8391,18 +8395,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr"/>
+          <t>إشارة إلى المادة (3)</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -8412,7 +8420,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -8429,18 +8437,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -8450,7 +8462,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -8467,18 +8479,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
+          <t>إشارة إلى المادة (21)</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -8488,7 +8504,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -8505,18 +8521,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
+          <t>إشارة إلى المادة (80)</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -8526,7 +8546,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8543,18 +8563,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -8564,7 +8588,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -8581,17 +8605,13 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -8606,7 +8626,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -8623,17 +8643,13 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -8648,7 +8664,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -8665,14 +8681,10 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة</t>
@@ -8690,7 +8702,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -8707,14 +8719,10 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة</t>
@@ -8732,7 +8740,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -8749,14 +8757,10 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة</t>
@@ -8774,7 +8778,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -8791,14 +8795,10 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة</t>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -8833,13 +8833,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -8854,7 +8858,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -8871,13 +8875,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr"/>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -8892,7 +8900,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -8909,13 +8917,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -8930,7 +8942,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -8947,13 +8959,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -8968,7 +8984,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -8985,17 +9001,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -9027,17 +9043,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9069,14 +9085,10 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
@@ -9094,7 +9106,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -9111,14 +9123,10 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
@@ -9136,7 +9144,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -9153,14 +9161,10 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
@@ -9178,7 +9182,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -9195,14 +9199,10 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -9237,13 +9237,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>تفاصيل شكوى المجلس الأعلى</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -9258,7 +9262,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -9275,13 +9279,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr"/>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -9296,7 +9304,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -9313,13 +9321,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -9334,7 +9346,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -9351,13 +9363,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -9372,7 +9388,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -9389,13 +9405,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -9410,7 +9430,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -9427,13 +9447,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -9448,7 +9472,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -9465,13 +9489,13 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -9503,7 +9527,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -9541,13 +9565,13 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -9579,13 +9603,13 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -9617,13 +9641,13 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -9655,13 +9679,13 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -9693,13 +9717,13 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -9731,13 +9755,13 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>نظام القضاء</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -9769,13 +9793,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -9790,7 +9818,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -9807,13 +9835,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr"/>
+          <t>إشارة إلى المادة (3)</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -9828,7 +9860,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -9845,13 +9877,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -9866,7 +9902,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -9883,13 +9919,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr"/>
+          <t>إشارة إلى المادة (21)</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -9904,7 +9944,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -9921,13 +9961,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr"/>
+          <t>إشارة إلى المادة (80)</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -9942,7 +9986,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -9959,13 +10003,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -9980,7 +10028,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -9997,13 +10045,13 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -10035,17 +10083,13 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -10060,7 +10104,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -10077,17 +10121,13 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -10102,7 +10142,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -10119,17 +10159,13 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -10144,7 +10180,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -10161,17 +10197,13 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (85)</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -10186,7 +10218,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -10203,17 +10235,13 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t>نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -10228,7 +10256,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -10245,13 +10273,13 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام القضاء</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10283,13 +10311,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -10304,7 +10336,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -10321,13 +10353,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr"/>
+          <t>إشارة إلى المادة (3)</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -10342,7 +10378,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -10359,13 +10395,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -10380,7 +10420,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -10397,13 +10437,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr"/>
+          <t>إشارة إلى المادة (21)</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -10418,7 +10462,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -10435,13 +10479,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
+          <t>إشارة إلى المادة (80)</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -10456,7 +10504,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -10473,13 +10521,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -10494,7 +10546,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -10511,13 +10563,13 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -10549,13 +10601,13 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -10587,13 +10639,13 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -10625,17 +10677,13 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -10650,7 +10698,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -10667,13 +10715,13 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -10705,13 +10753,13 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام القضاء</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -10743,13 +10791,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr"/>
+          <t>إشارة إلى المادة (3)</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -10764,7 +10816,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -10781,13 +10833,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr"/>
+          <t>إشارة إلى المادة (21)</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -10802,7 +10858,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -10819,13 +10875,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr"/>
+          <t>إشارة إلى المادة (80)</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -10840,7 +10900,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -10857,13 +10917,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr"/>
+          <t>إشارة إلى المادة (85)</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -10878,7 +10942,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -10895,13 +10959,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -10916,7 +10984,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -10933,13 +11001,13 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -10971,17 +11039,13 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (176)</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -10996,7 +11060,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -11013,18 +11077,18 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr">
         <is>
-          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -11051,18 +11115,18 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr">
         <is>
-          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -11089,22 +11153,18 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (176)</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr">
         <is>
-          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -11114,7 +11174,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -11131,18 +11191,18 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -11169,18 +11229,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -11190,7 +11254,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -11207,18 +11271,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr"/>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -11228,7 +11296,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -11245,18 +11313,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -11266,7 +11338,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -11283,18 +11355,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -11304,7 +11380,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -11321,18 +11397,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -11342,7 +11422,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -11359,18 +11439,22 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -11380,7 +11464,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -11397,18 +11481,18 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -11435,18 +11519,18 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -11473,18 +11557,18 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -11511,18 +11595,18 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -11549,18 +11633,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -11570,7 +11658,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -11587,18 +11675,18 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -11625,18 +11713,18 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -11663,18 +11751,18 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -11701,18 +11789,18 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -11739,22 +11827,18 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (175)</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -11764,7 +11848,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -11781,18 +11865,18 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -11819,18 +11903,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -11840,7 +11928,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -11857,18 +11945,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr"/>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -11878,7 +11970,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -11895,18 +11987,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -11916,7 +12012,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -11933,18 +12029,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -11954,7 +12054,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -11971,18 +12071,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -11992,7 +12096,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -12009,18 +12113,22 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -12030,7 +12138,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -12047,18 +12155,18 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -12085,18 +12193,18 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -12123,18 +12231,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr"/>
+          <t>إشارة إلى المادة (176)</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -12144,7 +12256,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -12161,18 +12273,18 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -12199,18 +12311,18 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -12237,18 +12349,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr"/>
+          <t>إشارة إلى المادة (176)</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -12258,7 +12374,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -12275,18 +12391,18 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -12313,18 +12429,18 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -12351,18 +12467,18 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -12389,18 +12505,18 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -12433,12 +12549,12 @@
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -12471,12 +12587,12 @@
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -12503,18 +12619,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -12524,7 +12644,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -12541,18 +12661,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -12562,7 +12686,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -12579,18 +12703,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -12600,7 +12728,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -12617,18 +12745,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -12638,7 +12770,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -12655,18 +12787,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -12676,7 +12812,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -12693,18 +12829,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد.docx</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -12714,7 +12854,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -12731,36 +12871,2626 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr"/>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr"/>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr"/>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (175)</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة (وورد)</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة (وورد)</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (8)</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (96)</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (100)</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr">
+        <is>
           <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
+      <c r="D376" t="inlineStr">
         <is>
           <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>ملخص الشكوى لولي العهد.docx</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
+++ b/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H377"/>
+  <dimension ref="A1:H364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1519,12 +1519,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (129)</t>
+          <t>إشارة إلى المادة (239)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1561,17 +1561,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (239)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (95)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1645,17 +1645,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (95)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+          <t>صحيفة دعوى عدنان ضد اسامة زيني ـ بطلان بيع حصة شركة احمد زيني التجارية الى اسامة زيني ـ 42824717 ـ 17-12-1442.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1670,7 +1666,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1687,7 +1683,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1725,13 +1721,13 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>صحيفة دعوى عدنان ضد اسامة زيني ـ بطلان بيع حصة شركة احمد زيني التجارية الى اسامة زيني ـ 42824717 ـ 17-12-1442.pdf</t>
+          <t>ملف دراسة دفع بعدم صفة المدعي/ عدنان في الدعوى لكون المورث قد امتدت حياته عقب العقد بسبع سنوات دون أن يطعن في العقد. ـ —</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1763,7 +1759,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1801,13 +1797,13 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ملف دراسة دفع بعدم صفة المدعي/ عدنان في الدعوى لكون المورث قد امتدت حياته عقب العقد بسبع سنوات دون أن يطعن في العقد. ـ —</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1839,7 +1835,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1877,7 +1873,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1915,7 +1911,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1953,7 +1949,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1991,10 +1987,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>إشارة إلى المادة (16)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (16)</t>
+          <t>إشارة إلى المادة (17)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2071,12 +2071,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (17)</t>
+          <t>إشارة إلى المادة (18)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (18)</t>
+          <t>إشارة إلى المادة (76)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (76)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2197,12 +2197,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (89)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2239,12 +2239,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (89)</t>
+          <t>إشارة إلى المادة (94)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2281,12 +2281,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (94)</t>
+          <t>إشارة إلى المادة (95)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (95)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2365,17 +2365,13 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام الشركات</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2390,7 +2386,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2407,13 +2403,13 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>نظام الشركات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2445,7 +2441,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2483,13 +2479,13 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2521,7 +2517,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2559,10 +2555,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>إشارة إلى المادة (170)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2597,17 +2597,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (170)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2639,22 +2639,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>نظام الشركات</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2664,7 +2660,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2681,13 +2677,13 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>نظام الشركات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2719,7 +2715,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2757,18 +2753,18 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2795,7 +2791,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2833,7 +2829,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2871,7 +2867,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2909,7 +2905,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2947,7 +2943,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2985,10 +2981,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>إشارة إلى المادة (17)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (17)</t>
+          <t>إشارة إلى المادة (18)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3065,12 +3065,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (18)</t>
+          <t>إشارة إلى المادة (25)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (25)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3149,12 +3149,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (88)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3191,12 +3191,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (88)</t>
+          <t>إشارة إلى المادة (93)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3233,12 +3233,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (93)</t>
+          <t>إشارة إلى المادة (194)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>194</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (194)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3317,17 +3317,13 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+          <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3342,7 +3338,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3359,7 +3355,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3397,7 +3393,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3435,7 +3431,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3473,10 +3469,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3511,12 +3511,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3553,12 +3553,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3637,12 +3637,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3679,12 +3679,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3721,17 +3721,13 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3746,7 +3742,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3763,7 +3759,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3801,13 +3797,13 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+          <t>ردود على حكم الالتماس 717</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3839,7 +3835,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3877,10 +3873,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>إشارة إلى المادة (17)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
           <t>ردود على حكم الالتماس 717</t>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (25)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3957,12 +3957,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (17)</t>
+          <t>إشارة إلى المادة (26)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3999,12 +3999,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (25)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4041,17 +4041,13 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ردود على حكم الالتماس 717</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4066,7 +4062,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4083,17 +4079,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ردود على حكم الالتماس 717</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4125,10 +4121,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>إشارة إلى المادة (16)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
           <t>طلب النقض على صك الاستئناف الثانية</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4163,12 +4163,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4205,12 +4205,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (16)</t>
+          <t>إشارة إلى المادة (85)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4247,17 +4247,13 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4272,7 +4268,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4289,17 +4285,13 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (85)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4314,7 +4306,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4331,13 +4323,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>إشارة إلى المادة (47)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4352,7 +4348,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4369,13 +4365,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>إشارة إلى المادة (69)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4407,17 +4407,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (230)</t>
+          <t>إشارة إلى المادة (78)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4449,12 +4449,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (47)</t>
+          <t>إشارة إلى المادة (185)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>185</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4491,17 +4491,13 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (69)</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4516,7 +4512,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4533,17 +4529,13 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4558,7 +4550,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4575,17 +4567,13 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (185)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4600,7 +4588,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4617,13 +4605,13 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4655,13 +4643,13 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4693,17 +4681,13 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (230)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4718,7 +4702,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4735,7 +4719,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4773,10 +4757,14 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>إشارة إلى المادة (26)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
           <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
@@ -4794,7 +4782,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4811,10 +4799,14 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>إشارة إلى المادة (78)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
           <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
@@ -4832,7 +4824,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4849,13 +4841,13 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4887,13 +4879,13 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4925,17 +4917,13 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4950,7 +4938,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4967,17 +4955,13 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4992,7 +4976,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5009,7 +4993,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -5047,10 +5031,14 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>إشارة إلى المادة (26)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
           <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
@@ -5068,7 +5056,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5085,10 +5073,14 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>إشارة إلى المادة (78)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
           <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
@@ -5106,7 +5098,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5123,13 +5115,13 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5161,13 +5153,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>إشارة إلى المادة (143)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5182,7 +5178,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5199,17 +5195,13 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5224,7 +5216,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5241,17 +5233,13 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5266,7 +5254,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5283,13 +5271,13 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5321,17 +5309,13 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (143)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5346,7 +5330,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5369,7 +5353,7 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5401,13 +5385,13 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5439,17 +5423,13 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (230)</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5464,7 +5444,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5481,13 +5461,13 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5519,13 +5499,13 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5557,17 +5537,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (230)</t>
+          <t>إشارة إلى المادة (26)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5599,10 +5579,14 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
           <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
@@ -5620,7 +5604,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5637,10 +5621,14 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
           <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
@@ -5658,7 +5646,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5675,13 +5663,13 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5713,13 +5701,13 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5751,13 +5739,13 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الشركات</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5789,17 +5777,13 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5814,7 +5798,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5831,17 +5815,13 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5856,7 +5836,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5873,17 +5853,13 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5898,7 +5874,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5915,7 +5891,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5953,7 +5929,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>النظام الاساسي للحكم</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5991,7 +5967,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>نظام الشركات</t>
+          <t>نظام القضاء</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -6029,10 +6005,14 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>إشارة إلى المادة (3)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
           <t>مذكرة طلب النقض على الحكم النهائي</t>
@@ -6050,7 +6030,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6067,10 +6047,14 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr">
         <is>
           <t>مذكرة طلب النقض على الحكم النهائي</t>
@@ -6088,7 +6072,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6105,10 +6089,14 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>إشارة إلى المادة (16)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
           <t>مذكرة طلب النقض على الحكم النهائي</t>
@@ -6126,7 +6114,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6143,10 +6131,14 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>إشارة إلى المادة (21)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr">
         <is>
           <t>مذكرة طلب النقض على الحكم النهائي</t>
@@ -6164,7 +6156,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6181,10 +6173,14 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>النظام الاساسي للحكم</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>إشارة إلى المادة (24)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr">
         <is>
           <t>مذكرة طلب النقض على الحكم النهائي</t>
@@ -6202,7 +6198,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6219,10 +6215,14 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>إشارة إلى المادة (26)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="C146" t="inlineStr">
         <is>
           <t>مذكرة طلب النقض على الحكم النهائي</t>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6257,12 +6257,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
+          <t>إشارة إلى المادة (76)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6299,12 +6299,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (78)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6341,12 +6341,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (16)</t>
+          <t>إشارة إلى المادة (80)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6383,12 +6383,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (85)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6425,12 +6425,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (24)</t>
+          <t>إشارة إلى المادة (88)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6467,12 +6467,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
+          <t>إشارة إلى المادة (141)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6509,12 +6509,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (76)</t>
+          <t>إشارة إلى المادة (162)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>162</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6551,17 +6551,13 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة نقض؟ .docx</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6576,7 +6572,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6593,17 +6589,13 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة نقض؟ .docx</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6618,7 +6610,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6635,17 +6627,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (85)</t>
+          <t>إشارة إلى المادة (17)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة نقض؟ .docx</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6677,17 +6669,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (88)</t>
+          <t>إشارة إلى المادة (25)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة نقض؟ .docx</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -6719,17 +6711,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
+          <t>إشارة إلى المادة (26)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة نقض؟ .docx</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -6761,17 +6753,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (162)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة نقض؟ .docx</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6803,10 +6795,14 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C160" t="inlineStr">
         <is>
           <t>مذكرة نقض؟ .docx</t>
@@ -6824,7 +6820,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6841,13 +6837,13 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الشركات</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>مذكرة نقض؟ .docx</t>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6879,17 +6875,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (17)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>مذكرة نقض؟ .docx</t>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -6921,17 +6917,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (25)</t>
+          <t>إشارة إلى المادة (165)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>مذكرة نقض؟ .docx</t>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -6963,17 +6959,13 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>مذكرة نقض؟ .docx</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -6988,7 +6980,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -7005,17 +6997,13 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>مذكرة نقض؟ .docx</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7030,7 +7018,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -7047,17 +7035,13 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>مذكرة نقض؟ .docx</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7072,7 +7056,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -7089,13 +7073,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>نظام الشركات</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7110,7 +7098,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7127,17 +7115,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (16)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7169,17 +7157,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (165)</t>
+          <t>إشارة إلى المادة (76)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7217,7 +7205,7 @@
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7255,7 +7243,7 @@
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7293,7 +7281,7 @@
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7325,17 +7313,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (33)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7367,17 +7355,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (16)</t>
+          <t>إشارة إلى المادة (76)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7409,22 +7397,18 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (76)</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -7434,7 +7418,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7451,18 +7435,18 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -7489,18 +7473,18 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -7527,18 +7511,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7548,7 +7536,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7565,22 +7553,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (16)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7607,22 +7595,18 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (33)</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7632,7 +7616,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7649,22 +7633,18 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (76)</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7674,7 +7654,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7691,13 +7671,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -7712,7 +7696,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -7729,13 +7713,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -7750,7 +7738,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7767,18 +7755,18 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>تفاصيل الشكوى</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7805,22 +7793,18 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7830,7 +7814,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7847,22 +7831,18 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7872,7 +7852,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7889,18 +7869,18 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -7927,18 +7907,18 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7965,22 +7945,18 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7990,7 +7966,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -8007,22 +7983,18 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -8032,7 +8004,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -8049,13 +8021,13 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام القضاء</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
-          <t>تفاصيل الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8087,10 +8059,14 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C192" t="inlineStr">
         <is>
           <t>الشكوى ومرفقاتها</t>
@@ -8108,7 +8084,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -8125,10 +8101,14 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr"/>
+          <t>إشارة إلى المادة (3)</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>الشكوى ومرفقاتها</t>
@@ -8146,7 +8126,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -8163,10 +8143,14 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>الشكوى ومرفقاتها</t>
@@ -8184,7 +8168,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8201,10 +8185,14 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr"/>
+          <t>إشارة إلى المادة (21)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>الشكوى ومرفقاتها</t>
@@ -8222,7 +8210,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -8239,10 +8227,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
+          <t>إشارة إلى المادة (80)</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>الشكوى ومرفقاتها</t>
@@ -8260,7 +8252,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -8277,10 +8269,14 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>الشكوى ومرفقاتها</t>
@@ -8298,7 +8294,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8315,18 +8311,18 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -8353,22 +8349,18 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -8378,7 +8370,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -8395,22 +8387,18 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -8420,7 +8408,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -8437,22 +8425,18 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -8462,7 +8446,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -8479,22 +8463,18 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -8504,7 +8484,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -8521,22 +8501,18 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -8546,7 +8522,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8563,22 +8539,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -8605,13 +8581,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr"/>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -8626,7 +8606,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -8643,13 +8623,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -8664,7 +8648,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -8681,10 +8665,14 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C207" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة</t>
@@ -8702,7 +8690,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -8719,10 +8707,14 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C208" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة</t>
@@ -8740,7 +8732,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -8757,10 +8749,14 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C209" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة</t>
@@ -8778,7 +8774,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -8795,13 +8791,13 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -8833,17 +8829,13 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -8858,7 +8850,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -8875,17 +8867,13 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -8900,7 +8888,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -8917,17 +8905,13 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -8942,7 +8926,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -8959,17 +8943,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -9001,17 +8985,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -9043,17 +9027,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9085,10 +9069,14 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C217" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
@@ -9106,7 +9094,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -9123,10 +9111,14 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C218" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
@@ -9144,7 +9136,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -9161,10 +9153,14 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C219" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
@@ -9182,7 +9178,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -9199,13 +9195,13 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -9237,17 +9233,13 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -9262,7 +9254,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -9279,17 +9271,13 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -9304,7 +9292,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -9321,17 +9309,13 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -9346,7 +9330,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -9363,17 +9347,13 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -9388,7 +9368,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -9405,17 +9385,13 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -9430,7 +9406,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -9447,17 +9423,13 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -9472,7 +9444,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -9489,13 +9461,13 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام القضاء</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
-          <t>تفاصيل شكوى المجلس الأعلى</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -9527,10 +9499,14 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C228" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
@@ -9548,7 +9524,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -9565,10 +9541,14 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr"/>
+          <t>إشارة إلى المادة (3)</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C229" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
@@ -9586,7 +9566,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -9603,10 +9583,14 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C230" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
@@ -9624,7 +9608,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -9641,10 +9625,14 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr"/>
+          <t>إشارة إلى المادة (21)</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="C231" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
@@ -9662,7 +9650,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -9679,10 +9667,14 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr"/>
+          <t>إشارة إلى المادة (80)</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="C232" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
@@ -9700,7 +9692,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -9717,10 +9709,14 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C233" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
@@ -9738,7 +9734,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -9755,13 +9751,13 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -9793,17 +9789,13 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -9818,7 +9810,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -9835,17 +9827,13 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -9860,7 +9848,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -9877,17 +9865,13 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -9902,7 +9886,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -9919,17 +9903,13 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -9944,7 +9924,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -9961,17 +9941,13 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -9986,7 +9962,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -10003,17 +9979,13 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t>نظام القضاء</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -10028,7 +10000,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -10045,10 +10017,14 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C241" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
@@ -10066,7 +10042,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -10083,10 +10059,14 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr"/>
+          <t>إشارة إلى المادة (3)</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C242" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
@@ -10104,7 +10084,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -10121,10 +10101,14 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C243" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
@@ -10142,7 +10126,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -10159,10 +10143,14 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr"/>
+          <t>إشارة إلى المادة (21)</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="C244" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
@@ -10180,7 +10168,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -10197,10 +10185,14 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr"/>
+          <t>إشارة إلى المادة (80)</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="C245" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
@@ -10218,7 +10210,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -10235,10 +10227,14 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C246" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
@@ -10256,7 +10252,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -10273,13 +10269,13 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10311,17 +10307,13 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -10336,7 +10328,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -10353,17 +10345,13 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -10378,7 +10366,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -10395,17 +10383,13 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -10420,7 +10404,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -10437,17 +10421,13 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -10462,7 +10442,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -10479,17 +10459,13 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>نظام القضاء</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -10504,7 +10480,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -10521,17 +10497,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -10563,10 +10539,14 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr"/>
+          <t>إشارة إلى المادة (80)</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="C254" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
@@ -10584,7 +10564,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -10601,10 +10581,14 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr"/>
+          <t>إشارة إلى المادة (85)</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="C255" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
@@ -10622,7 +10606,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -10639,10 +10623,14 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C256" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
@@ -10660,7 +10648,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -10677,13 +10665,13 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -10715,13 +10703,13 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -10753,13 +10741,13 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -10791,17 +10779,13 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -10816,7 +10800,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -10833,17 +10817,13 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -10858,7 +10838,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -10875,17 +10855,13 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -10900,7 +10876,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -10917,17 +10893,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (85)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -10959,17 +10935,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -11001,10 +10977,14 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C265" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
@@ -11022,7 +11002,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -11039,10 +11019,14 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C266" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
@@ -11060,7 +11044,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -11077,10 +11061,14 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C267" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
@@ -11098,7 +11086,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -11115,10 +11103,14 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C268" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
@@ -11136,7 +11128,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -11153,13 +11145,13 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -11191,13 +11183,13 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -11229,17 +11221,13 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -11254,7 +11242,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -11271,17 +11259,13 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -11296,7 +11280,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -11313,17 +11297,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -11355,17 +11339,13 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -11380,7 +11360,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -11397,17 +11377,13 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -11422,7 +11398,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -11439,17 +11415,13 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -11464,7 +11436,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -11481,13 +11453,13 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -11519,13 +11491,13 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -11557,13 +11529,13 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -11595,13 +11567,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -11616,7 +11592,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -11633,17 +11609,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -11675,10 +11651,14 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C282" t="inlineStr">
         <is>
           <t>ملف مؤقت tmp</t>
@@ -11696,7 +11676,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -11713,10 +11693,14 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C283" t="inlineStr">
         <is>
           <t>ملف مؤقت tmp</t>
@@ -11734,7 +11718,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -11751,10 +11735,14 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C284" t="inlineStr">
         <is>
           <t>ملف مؤقت tmp</t>
@@ -11772,7 +11760,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -11789,10 +11777,14 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C285" t="inlineStr">
         <is>
           <t>ملف مؤقت tmp</t>
@@ -11810,7 +11802,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -11827,13 +11819,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr"/>
+          <t>إشارة إلى المادة (176)</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -11848,7 +11844,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -11865,18 +11861,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr"/>
+          <t>إشارة إلى المادة (176)</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -11903,22 +11903,18 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -11928,7 +11924,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -11945,22 +11941,18 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -11970,7 +11962,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -11987,22 +11979,18 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -12012,7 +12000,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -12029,22 +12017,18 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -12054,7 +12038,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -12071,22 +12055,18 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -12096,7 +12076,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -12113,22 +12093,18 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -12138,7 +12114,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -12155,18 +12131,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -12176,7 +12156,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -12193,18 +12173,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr"/>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -12214,7 +12198,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -12231,22 +12215,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (176)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -12273,13 +12257,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -12294,7 +12282,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -12311,13 +12299,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -12332,7 +12324,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -12349,17 +12341,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (176)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -12397,7 +12389,7 @@
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -12435,7 +12427,7 @@
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -12473,7 +12465,7 @@
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -12511,7 +12503,7 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -12549,7 +12541,7 @@
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -12587,7 +12579,7 @@
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -12629,7 +12621,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -12671,7 +12663,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -12713,7 +12705,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -12755,7 +12747,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -12797,7 +12789,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -12839,7 +12831,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -12871,13 +12863,13 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -12909,13 +12901,13 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -12947,13 +12939,13 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -12985,13 +12977,13 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -13023,13 +13015,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr"/>
+          <t>إشارة إلى المادة (175)</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -13044,7 +13040,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -13061,18 +13057,18 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -13099,22 +13095,18 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -13124,7 +13116,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -13141,22 +13133,18 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -13166,7 +13154,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -13183,22 +13171,18 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -13208,7 +13192,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -13225,22 +13209,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -13267,22 +13251,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -13309,22 +13293,22 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -13351,18 +13335,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -13372,7 +13360,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -13389,18 +13377,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -13410,7 +13402,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -13427,18 +13419,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -13448,7 +13444,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -13465,18 +13461,18 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -13503,22 +13499,18 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (175)</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -13528,7 +13520,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -13545,18 +13537,18 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -13583,18 +13575,18 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -13621,18 +13613,18 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -13659,18 +13651,18 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -13697,22 +13689,18 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -13722,7 +13710,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -13739,22 +13727,18 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -13764,7 +13748,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -13781,22 +13765,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -13823,22 +13807,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -13865,22 +13849,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -13907,22 +13891,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -13949,18 +13933,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -13970,7 +13958,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -13987,18 +13975,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -14008,7 +14000,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -14025,18 +14017,18 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -14063,18 +14055,18 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -14101,18 +14093,18 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -14139,18 +14131,18 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -14177,18 +14169,18 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -14215,18 +14207,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -14236,7 +14232,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -14253,22 +14249,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (8)</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -14295,22 +14291,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (100)</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -14337,22 +14333,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -14379,22 +14375,18 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -14404,7 +14396,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -14421,22 +14413,18 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -14446,7 +14434,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -14463,22 +14451,18 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -14488,7 +14472,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -14505,13 +14489,13 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -14549,7 +14533,7 @@
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -14587,7 +14571,7 @@
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -14619,13 +14603,13 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -14657,13 +14641,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -14678,7 +14666,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -14695,17 +14683,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -14737,17 +14725,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (8)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -14779,17 +14767,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (96)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -14821,17 +14809,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (100)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -14873,7 +14861,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -14911,7 +14899,7 @@
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -14949,7 +14937,7 @@
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -14973,524 +14961,6 @@
         </is>
       </c>
       <c r="H364" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr"/>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr"/>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr"/>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr"/>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr"/>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
-        </is>
-      </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
-        </is>
-      </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>مرفقات الشكوى</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr"/>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>ملخص الشكوى لولي العهد.docx</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr"/>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>ملخص الشكوى لولي العهد.docx</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H377" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
+++ b/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H475"/>
+  <dimension ref="A1:H488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2195,7 +2195,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2233,14 +2233,10 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
@@ -2258,7 +2254,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2275,13 +2271,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>نظام الشركات</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>صك حكم التخارج في شركات احمد زيني و اولاده ـ 02-12-1432 هـ.pdf</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2313,13 +2313,13 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الشركات</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>صك حكم التخارج في شركات احمد زيني و اولاده ـ 02-12-1432 هـ.pdf</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2351,7 +2351,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2389,7 +2389,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2427,7 +2427,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2465,7 +2465,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2503,14 +2503,10 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
@@ -2528,7 +2524,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2545,12 +2541,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
+          <t>إشارة إلى المادة (26)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2587,12 +2583,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (104)</t>
+          <t>إشارة إلى المادة (78)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2629,13 +2625,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>إشارة إلى المادة (104)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2667,14 +2667,10 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (88)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
@@ -2692,7 +2688,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2709,12 +2705,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (90)</t>
+          <t>إشارة إلى المادة (88)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2751,13 +2747,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>إشارة إلى المادة (90)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2789,7 +2789,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2827,14 +2827,10 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
@@ -2852,7 +2848,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2869,13 +2865,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2907,7 +2907,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2945,14 +2945,10 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
@@ -2970,7 +2966,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2987,12 +2983,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (5)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3029,12 +3025,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (5)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3071,12 +3067,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3113,12 +3109,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (79)</t>
+          <t>إشارة إلى المادة (78)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3155,12 +3151,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (239)</t>
+          <t>إشارة إلى المادة (79)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3197,17 +3193,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (239)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3239,12 +3235,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (95)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3281,13 +3277,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>إشارة إلى المادة (95)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>صحيفة دعوى عدنان ضد اسامة زيني ـ بطلان بيع حصة شركة احمد زيني التجارية الى اسامة زيني ـ 42824717 ـ 17-12-1442.pdf</t>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3357,13 +3357,13 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ملف دراسة دفع بعدم صفة المدعي/ عدنان في الدعوى لكون المورث قد امتدت حياته عقب العقد بسبع سنوات دون أن يطعن في العقد. ـ —</t>
+          <t>صحيفة دعوى عدنان ضد اسامة زيني ـ بطلان بيع حصة شركة احمد زيني التجارية الى اسامة زيني ـ 42824717 ـ 17-12-1442.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3395,7 +3395,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3433,13 +3433,13 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
+          <t>ملف دراسة دفع بعدم صفة المدعي/ عدنان في الدعوى لكون المورث قد امتدت حياته عقب العقد بسبع سنوات دون أن يطعن في العقد. ـ —</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3471,7 +3471,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3547,7 +3547,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3585,7 +3585,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3623,14 +3623,10 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (16)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
@@ -3648,7 +3644,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3665,12 +3661,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (17)</t>
+          <t>إشارة إلى المادة (16)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3707,12 +3703,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (18)</t>
+          <t>إشارة إلى المادة (17)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3749,12 +3745,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (76)</t>
+          <t>إشارة إلى المادة (18)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3791,12 +3787,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (76)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3833,12 +3829,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (89)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3875,12 +3871,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (94)</t>
+          <t>إشارة إلى المادة (89)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3917,12 +3913,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (95)</t>
+          <t>إشارة إلى المادة (94)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3959,12 +3955,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (95)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4001,13 +3997,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>نظام الشركات</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4039,13 +4039,13 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الشركات</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -4115,13 +4115,13 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4191,14 +4191,10 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (170)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
           <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
@@ -4216,7 +4212,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4233,17 +4229,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (170)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>170</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4275,18 +4271,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>نظام الشركات</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4313,13 +4313,13 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الشركات</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4351,7 +4351,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4389,18 +4389,18 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4427,7 +4427,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4465,7 +4465,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4503,7 +4503,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4541,7 +4541,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4579,7 +4579,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4617,14 +4617,10 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (17)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
           <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
@@ -4642,7 +4638,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4659,12 +4655,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (18)</t>
+          <t>إشارة إلى المادة (17)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4701,12 +4697,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (25)</t>
+          <t>إشارة إلى المادة (18)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4743,12 +4739,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (25)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4785,12 +4781,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (88)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4827,12 +4823,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (93)</t>
+          <t>إشارة إلى المادة (88)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4869,12 +4865,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (194)</t>
+          <t>إشارة إلى المادة (93)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4911,12 +4907,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (194)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>194</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4953,13 +4949,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4991,7 +4991,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -5029,7 +5029,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -5105,14 +5105,10 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
@@ -5130,7 +5126,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5147,12 +5143,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5189,12 +5185,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5231,12 +5227,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5273,12 +5269,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5315,12 +5311,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5357,13 +5353,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5395,7 +5395,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5433,13 +5433,13 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5471,7 +5471,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5509,7 +5509,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5547,7 +5547,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5585,7 +5585,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5623,14 +5623,10 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (01)</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
+          <t>نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
@@ -5648,7 +5644,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5665,12 +5661,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
+          <t>إشارة إلى المادة (01)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5707,12 +5703,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (4)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5749,12 +5745,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (15)</t>
+          <t>إشارة إلى المادة (4)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5791,12 +5787,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (17)</t>
+          <t>إشارة إلى المادة (15)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5833,12 +5829,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (29)</t>
+          <t>إشارة إلى المادة (17)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5875,12 +5871,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (57)</t>
+          <t>إشارة إلى المادة (29)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5917,12 +5913,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (69)</t>
+          <t>إشارة إلى المادة (57)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5959,12 +5955,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (159)</t>
+          <t>إشارة إلى المادة (69)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6001,13 +5997,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>إشارة إلى المادة (159)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -6039,7 +6039,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -6077,7 +6077,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -6115,7 +6115,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -6153,7 +6153,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -6191,7 +6191,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -6229,14 +6229,10 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
           <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
@@ -6254,7 +6250,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6271,12 +6267,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (9)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6313,12 +6309,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (17)</t>
+          <t>إشارة إلى المادة (9)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6355,12 +6351,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (28)</t>
+          <t>إشارة إلى المادة (17)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6397,12 +6393,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (87)</t>
+          <t>إشارة إلى المادة (28)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6439,12 +6435,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (184)</t>
+          <t>إشارة إلى المادة (87)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6481,12 +6477,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (190)</t>
+          <t>إشارة إلى المادة (184)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>184</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6523,12 +6519,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (190)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>190</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6565,13 +6561,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ردود على حكم الالتماس 717</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6641,14 +6641,10 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (17)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
           <t>ردود على حكم الالتماس 717</t>
@@ -6666,7 +6662,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6683,12 +6679,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (25)</t>
+          <t>إشارة إلى المادة (17)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6725,12 +6721,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
+          <t>إشارة إلى المادة (25)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6767,12 +6763,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (26)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6809,13 +6805,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>ردود على حكم الالتماس 717</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6847,14 +6847,10 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
           <t>طلب النقض على صك الاستئناف الثانية</t>
@@ -6872,7 +6868,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6889,12 +6885,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (16)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6931,12 +6927,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (16)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6973,12 +6969,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (85)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7015,13 +7011,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
+          <t>إشارة إلى المادة (85)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -7053,7 +7053,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -7091,17 +7091,13 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (47)</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7116,7 +7112,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -7133,12 +7129,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (69)</t>
+          <t>إشارة إلى المادة (47)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7175,12 +7171,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
+          <t>إشارة إلى المادة (69)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7217,12 +7213,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (185)</t>
+          <t>إشارة إلى المادة (78)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10887,12 +10883,12 @@
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -10925,12 +10921,12 @@
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -10963,12 +10959,12 @@
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -10995,22 +10991,18 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -11020,7 +11012,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -11037,22 +11029,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (08)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -11079,18 +11071,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr"/>
+          <t>إشارة إلى المادة (47)</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -11100,7 +11096,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -11117,18 +11113,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr"/>
+          <t>إشارة إلى المادة (51)</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -11155,22 +11155,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (69)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -11197,22 +11197,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (78)</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -11239,18 +11239,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>تفاصيل الشكوى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -11260,7 +11264,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -11277,18 +11281,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -11298,7 +11306,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -11315,18 +11323,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -11336,7 +11348,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -11353,18 +11365,18 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -11391,18 +11403,18 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -11429,18 +11441,18 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -11467,18 +11479,22 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -11488,7 +11504,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -11505,18 +11521,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -11526,7 +11546,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -11543,22 +11563,18 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -11568,7 +11584,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -11585,22 +11601,18 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -11610,7 +11622,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -11627,22 +11639,22 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -11669,22 +11681,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -11711,17 +11723,13 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>تفاصيل الشكوى</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -11736,7 +11744,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -11753,14 +11761,10 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
         <is>
           <t>الشكوى ومرفقاتها</t>
@@ -11778,7 +11782,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -11795,18 +11799,18 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -11833,18 +11837,18 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -11871,18 +11875,18 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -11909,18 +11913,18 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -11947,18 +11951,18 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -11985,18 +11989,18 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام القضاء</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -12033,12 +12037,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -12065,22 +12069,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -12107,22 +12111,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -12149,22 +12153,22 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -12191,22 +12195,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (80)</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -12233,22 +12237,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (141)</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -12275,13 +12279,13 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -12313,13 +12317,13 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -12351,13 +12355,13 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -12389,13 +12393,13 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -12427,17 +12431,13 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -12469,17 +12469,13 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -12494,7 +12490,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -12511,17 +12507,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -12553,17 +12549,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -12595,17 +12591,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -12637,17 +12633,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -12679,13 +12675,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>تفاصيل شكوى المجلس الأعلى</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -12717,13 +12717,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -12738,7 +12742,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -12755,13 +12759,13 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -12793,13 +12797,13 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -12831,13 +12835,13 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
       <c r="C310" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -12869,13 +12873,13 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -12907,13 +12911,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -12928,7 +12936,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -12945,13 +12953,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr"/>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -12966,7 +12978,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -12983,17 +12995,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -13025,17 +13037,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -13067,17 +13079,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -13109,17 +13121,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -13151,17 +13163,13 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -13176,7 +13184,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -13193,14 +13201,10 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
@@ -13218,7 +13222,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -13235,13 +13239,13 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -13273,13 +13277,13 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -13311,13 +13315,13 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -13349,13 +13353,13 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
       <c r="C323" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -13387,13 +13391,13 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -13425,13 +13429,13 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>نظام القضاء</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -13463,13 +13467,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -13484,7 +13492,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -13501,17 +13509,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -13543,17 +13551,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -13585,17 +13593,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -13627,17 +13635,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (80)</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -13669,17 +13677,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
+          <t>إشارة إلى المادة (141)</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -13711,14 +13719,10 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
@@ -13736,7 +13740,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -13753,13 +13757,13 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -13791,13 +13795,13 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -13829,13 +13833,13 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
       <c r="C335" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -13867,13 +13871,13 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -13905,13 +13909,13 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -13949,7 +13953,7 @@
       <c r="B338" t="inlineStr"/>
       <c r="C338" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -13981,17 +13985,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -14023,17 +14027,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -14065,17 +14069,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (85)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -14107,17 +14111,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -14149,13 +14153,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr"/>
+          <t>إشارة إلى المادة (80)</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -14170,7 +14178,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -14187,13 +14195,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -14208,7 +14220,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -14225,13 +14237,13 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -14263,13 +14275,13 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -14301,13 +14313,13 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -14339,13 +14351,13 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
       <c r="C348" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -14377,17 +14389,13 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -14402,7 +14410,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -14419,17 +14427,13 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>نظام القضاء</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -14444,7 +14448,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -14461,17 +14465,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -14503,17 +14507,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (80)</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -14545,17 +14549,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (85)</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -14587,17 +14591,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (141)</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -14635,7 +14639,7 @@
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -14673,7 +14677,7 @@
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -14705,13 +14709,13 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>نظام الشركات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -14743,13 +14747,13 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
       <c r="C358" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -14781,13 +14785,13 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -14819,13 +14823,13 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -14857,13 +14861,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -14878,7 +14886,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -14895,17 +14903,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -14937,17 +14945,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (2)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -14979,17 +14987,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (8)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -15021,17 +15029,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (16)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -15063,17 +15071,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (19)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -15105,14 +15113,10 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (20)</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
       <c r="C367" t="inlineStr">
         <is>
           <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
@@ -15130,7 +15134,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -15147,14 +15151,10 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
       <c r="C368" t="inlineStr">
         <is>
           <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -15189,14 +15189,10 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (25)</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>نظام الشركات</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
       <c r="C369" t="inlineStr">
         <is>
           <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
@@ -15214,7 +15210,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -15231,14 +15227,10 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr">
         <is>
           <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
@@ -15256,7 +15248,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -15273,14 +15265,10 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (29)</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr">
         <is>
           <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
@@ -15298,7 +15286,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -15315,14 +15303,10 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (40)</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
       <c r="C372" t="inlineStr">
         <is>
           <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
@@ -15340,7 +15324,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -15357,14 +15341,10 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (41)</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr">
         <is>
           <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
@@ -15382,7 +15362,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -15399,12 +15379,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (76)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -15441,12 +15421,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
+          <t>إشارة إلى المادة (2)</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -15483,12 +15463,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (87)</t>
+          <t>إشارة إلى المادة (8)</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -15525,12 +15505,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (93)</t>
+          <t>إشارة إلى المادة (16)</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -15567,12 +15547,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (157)</t>
+          <t>إشارة إلى المادة (19)</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -15609,12 +15589,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (158)</t>
+          <t>إشارة إلى المادة (20)</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -15651,12 +15631,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (165)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -15693,13 +15673,17 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr"/>
+          <t>إشارة إلى المادة (25)</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -15714,7 +15698,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -15731,13 +15715,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr"/>
+          <t>إشارة إلى المادة (26)</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -15752,7 +15740,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -15769,13 +15757,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr"/>
+          <t>إشارة إلى المادة (29)</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -15790,7 +15782,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -15807,17 +15799,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (40)</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -15849,13 +15841,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr"/>
+          <t>إشارة إلى المادة (41)</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -15870,7 +15866,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -15887,13 +15883,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr"/>
+          <t>إشارة إلى المادة (66)</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -15925,13 +15925,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr"/>
+          <t>إشارة إلى المادة (76)</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -15946,7 +15950,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -15963,13 +15967,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr"/>
+          <t>إشارة إلى المادة (78)</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -15984,7 +15992,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -16001,13 +16009,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr"/>
+          <t>إشارة إلى المادة (87)</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -16022,7 +16034,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -16039,13 +16051,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr"/>
+          <t>إشارة إلى المادة (93)</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -16060,7 +16076,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -16077,17 +16093,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (157)</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>157</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -16119,17 +16135,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (158)</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -16161,17 +16177,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (165)</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -16203,17 +16219,13 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
       <c r="C394" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -16228,7 +16240,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -16245,17 +16257,13 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
       <c r="C395" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -16270,7 +16278,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -16287,17 +16295,13 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -16312,7 +16316,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -16329,17 +16333,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (176)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -16371,22 +16375,18 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (176)</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
       <c r="C398" t="inlineStr">
         <is>
-          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -16413,18 +16413,18 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
       <c r="C399" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -16451,18 +16451,18 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
       <c r="C400" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -16489,18 +16489,18 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
       <c r="C401" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -16527,18 +16527,18 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
       <c r="C402" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -16565,18 +16565,18 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -16603,18 +16603,22 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -16624,7 +16628,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -16641,22 +16645,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -16683,22 +16687,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -16725,22 +16729,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -16767,22 +16771,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -16809,22 +16813,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -16851,22 +16855,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (176)</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>176</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -16893,13 +16897,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr"/>
+          <t>إشارة إلى المادة (176)</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -16914,7 +16922,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -16931,13 +16939,13 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
       <c r="C412" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -16969,13 +16977,13 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
       <c r="C413" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -17007,13 +17015,13 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
       <c r="C414" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -17045,13 +17053,13 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
       <c r="C415" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -17083,13 +17091,13 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
       <c r="C416" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -17121,17 +17129,13 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -17146,7 +17150,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -17163,17 +17167,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -17205,17 +17209,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -17247,17 +17251,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -17289,17 +17293,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -17331,17 +17335,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -17373,13 +17377,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -17394,7 +17402,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -17411,13 +17419,13 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
       <c r="C424" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -17449,13 +17457,13 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -17493,7 +17501,7 @@
       <c r="B426" t="inlineStr"/>
       <c r="C426" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -17525,17 +17533,13 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (175)</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -17550,7 +17554,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -17567,18 +17571,18 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -17605,18 +17609,18 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
       <c r="C429" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -17643,18 +17647,22 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -17664,7 +17672,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -17681,18 +17689,22 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr"/>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -17702,7 +17714,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -17719,22 +17731,22 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -17761,22 +17773,22 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -17803,22 +17815,22 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -17845,22 +17857,22 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -17887,22 +17899,18 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -17912,7 +17920,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -17929,22 +17937,18 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
       <c r="C437" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -17954,7 +17958,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
@@ -17971,18 +17975,18 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
       <c r="C438" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -18009,18 +18013,18 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
       <c r="C439" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -18047,18 +18051,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr"/>
+          <t>إشارة إلى المادة (175)</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -18068,7 +18076,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -18085,18 +18093,18 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
       <c r="C441" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -18123,18 +18131,18 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
       <c r="C442" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -18161,18 +18169,18 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
       <c r="C443" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -18199,18 +18207,18 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
       <c r="C444" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -18237,18 +18245,22 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr"/>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -18258,7 +18270,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -18275,22 +18287,22 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -18317,22 +18329,22 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -18359,22 +18371,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -18401,22 +18413,22 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -18443,22 +18455,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -18485,22 +18497,18 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
       <c r="C451" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -18510,7 +18518,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -18527,18 +18535,18 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
       <c r="C452" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -18565,18 +18573,18 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -18603,18 +18611,18 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
       <c r="C454" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -18641,18 +18649,18 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -18679,18 +18687,18 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
       <c r="C456" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -18717,22 +18725,18 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
       <c r="C457" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -18742,7 +18746,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -18759,22 +18763,18 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (8)</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -18784,7 +18784,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -18801,22 +18801,22 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (100)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -18843,22 +18843,22 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -18885,18 +18885,22 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr"/>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -18906,7 +18910,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
@@ -18923,18 +18927,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -18944,7 +18952,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -18961,18 +18969,22 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -18982,7 +18994,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -18999,18 +19011,22 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -19020,7 +19036,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -19037,13 +19053,13 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
       <c r="C465" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -19075,13 +19091,13 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
       <c r="C466" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -19113,13 +19129,13 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
       <c r="C467" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -19151,17 +19167,13 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
       <c r="C468" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -19176,7 +19188,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -19193,17 +19205,13 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
       <c r="C469" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -19218,7 +19226,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -19235,17 +19243,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -19277,17 +19285,17 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (8)</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -19319,17 +19327,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (100)</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -19371,7 +19379,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -19409,7 +19417,7 @@
       <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد.docx</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -19447,30 +19455,548 @@
       <c r="B475" t="inlineStr"/>
       <c r="C475" t="inlineStr">
         <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>نظام المرافعات الشرعية</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>نظام المحاكم التجارية</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (1)</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (58)</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (86)</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>نظام الاثبات</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr"/>
+      <c r="C487" t="inlineStr">
+        <is>
           <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
+      <c r="D487" t="inlineStr">
         <is>
           <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>يحتاج تحقق رسمي</t>
-        </is>
-      </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
-        </is>
-      </c>
-      <c r="G475" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="H475" t="inlineStr">
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr"/>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>ملخص الشكوى لولي العهد.docx</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
+++ b/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H488"/>
+  <dimension ref="A1:H489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10229,12 +10229,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (33)</t>
+          <t>إشارة إلى المادة (16)</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -10271,12 +10271,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (76)</t>
+          <t>إشارة إلى المادة (33)</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -10313,18 +10313,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr"/>
+          <t>إشارة إلى المادة (76)</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -10334,7 +10338,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -10351,7 +10355,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -10389,7 +10393,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -10427,7 +10431,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -10465,7 +10469,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -10503,7 +10507,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -10541,14 +10545,10 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (25)</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
         <is>
           <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -10583,12 +10583,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
+          <t>إشارة إلى المادة (25)</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -10625,12 +10625,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (29)</t>
+          <t>إشارة إلى المادة (26)</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -10667,12 +10667,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (40)</t>
+          <t>إشارة إلى المادة (29)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -10709,12 +10709,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (41)</t>
+          <t>إشارة إلى المادة (40)</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -10751,12 +10751,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (76)</t>
+          <t>إشارة إلى المادة (41)</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -10793,12 +10793,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (76)</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -10835,12 +10835,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (87)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10877,18 +10877,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr"/>
+          <t>إشارة إلى المادة (87)</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -10898,7 +10902,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -10915,7 +10919,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -10953,7 +10957,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -10991,7 +10995,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -11029,14 +11033,10 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (08)</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr">
         <is>
           <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -11071,12 +11071,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (47)</t>
+          <t>إشارة إلى المادة (08)</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -11113,12 +11113,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (51)</t>
+          <t>إشارة إلى المادة (47)</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -11155,12 +11155,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (69)</t>
+          <t>إشارة إلى المادة (51)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -11197,12 +11197,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
+          <t>إشارة إلى المادة (69)</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -11239,12 +11239,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (78)</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -11281,12 +11281,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -11323,12 +11323,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -11365,18 +11365,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -11386,7 +11390,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -11403,7 +11407,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -11441,7 +11445,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -11479,14 +11483,10 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
         <is>
           <t>التماس ضد الحكم ـ نسخة أولى</t>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -11521,12 +11521,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -11563,13 +11563,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr"/>
+          <t>إشارة إلى المادة (200)</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -11584,7 +11588,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -11601,7 +11605,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -11639,14 +11643,10 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
           <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -11681,12 +11681,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -11723,18 +11723,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr"/>
+          <t>إشارة إلى المادة (201)</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>تفاصيل الشكوى</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -11744,7 +11748,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -11761,13 +11765,13 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>تفاصيل الشكوى</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -11799,7 +11803,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -11837,7 +11841,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -11875,7 +11879,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -11913,7 +11917,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -11951,7 +11955,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -11989,7 +11993,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -12027,14 +12031,10 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام القضاء</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
           <t>الشكوى ومرفقاتها</t>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -12069,12 +12069,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12111,12 +12111,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -12153,12 +12153,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -12195,12 +12195,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -12237,12 +12237,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
+          <t>إشارة إلى المادة (80)</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -12279,18 +12279,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -12300,7 +12304,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -12317,7 +12321,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -12355,13 +12359,13 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -12393,7 +12397,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -12431,7 +12435,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -12469,7 +12473,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -12507,14 +12511,10 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة</t>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -12549,12 +12549,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -12591,12 +12591,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -12633,12 +12633,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -12675,12 +12675,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -12717,12 +12717,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -12759,13 +12759,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -12780,7 +12784,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -12797,7 +12801,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -12835,7 +12839,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -12873,7 +12877,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -12911,14 +12915,10 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
           <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -12953,12 +12953,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12995,12 +12995,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -13037,12 +13037,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -13079,12 +13079,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -13121,12 +13121,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -13163,13 +13163,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>تفاصيل شكوى المجلس الأعلى</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -13184,7 +13188,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -13201,13 +13205,13 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -13239,7 +13243,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -13277,7 +13281,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -13315,7 +13319,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -13353,7 +13357,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -13391,7 +13395,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -13429,7 +13433,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -13467,14 +13471,10 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام القضاء</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -13509,12 +13509,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -13551,12 +13551,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -13593,12 +13593,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -13635,12 +13635,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -13677,12 +13677,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
+          <t>إشارة إلى المادة (80)</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -13719,13 +13719,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -13740,7 +13744,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -13757,7 +13761,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -13795,7 +13799,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -13833,7 +13837,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -13871,7 +13875,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -13909,7 +13913,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -13947,7 +13951,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام التنفيذ</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -13985,14 +13989,10 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام القضاء</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
       <c r="C339" t="inlineStr">
         <is>
           <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -14027,12 +14027,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (3)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -14069,12 +14069,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
+          <t>إشارة إلى المادة (3)</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -14111,12 +14111,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (6)</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -14153,12 +14153,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -14195,12 +14195,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
+          <t>إشارة إلى المادة (80)</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -14237,13 +14237,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -14258,7 +14262,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -14275,7 +14279,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -14313,7 +14317,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -14351,7 +14355,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -14389,7 +14393,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -14427,7 +14431,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>نظام القضاء</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -14465,14 +14469,10 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>نظام القضاء</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -14507,12 +14507,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (80)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -14549,12 +14549,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (85)</t>
+          <t>إشارة إلى المادة (80)</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -14591,12 +14591,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (141)</t>
+          <t>إشارة إلى المادة (85)</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -14633,13 +14633,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr"/>
+          <t>إشارة إلى المادة (141)</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -14654,7 +14658,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -14671,7 +14675,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -14709,7 +14713,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -14747,7 +14751,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -14785,7 +14789,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -14823,7 +14827,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -14861,14 +14865,10 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -14903,12 +14903,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -14945,12 +14945,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -14987,12 +14987,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -15029,12 +15029,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -15071,12 +15071,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -15113,13 +15113,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -15134,7 +15138,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -15151,7 +15155,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -15189,7 +15193,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>نظام الشركات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -15227,7 +15231,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام الشركات</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -15265,7 +15269,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -15303,7 +15307,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -15341,7 +15345,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -15379,14 +15383,10 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
       <c r="C374" t="inlineStr">
         <is>
           <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
@@ -15404,7 +15404,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -15421,12 +15421,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (2)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -15463,12 +15463,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (8)</t>
+          <t>إشارة إلى المادة (2)</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -15505,12 +15505,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (16)</t>
+          <t>إشارة إلى المادة (8)</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -15547,12 +15547,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (19)</t>
+          <t>إشارة إلى المادة (16)</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -15589,12 +15589,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (20)</t>
+          <t>إشارة إلى المادة (19)</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -15631,12 +15631,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (21)</t>
+          <t>إشارة إلى المادة (20)</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -15673,12 +15673,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (25)</t>
+          <t>إشارة إلى المادة (21)</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -15715,12 +15715,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (26)</t>
+          <t>إشارة إلى المادة (25)</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -15757,12 +15757,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (29)</t>
+          <t>إشارة إلى المادة (26)</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -15799,12 +15799,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (40)</t>
+          <t>إشارة إلى المادة (29)</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -15841,12 +15841,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (41)</t>
+          <t>إشارة إلى المادة (40)</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -15883,12 +15883,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (66)</t>
+          <t>إشارة إلى المادة (41)</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -15925,12 +15925,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (76)</t>
+          <t>إشارة إلى المادة (66)</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -15967,12 +15967,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (78)</t>
+          <t>إشارة إلى المادة (76)</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -16009,12 +16009,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (87)</t>
+          <t>إشارة إلى المادة (78)</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -16051,12 +16051,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (93)</t>
+          <t>إشارة إلى المادة (87)</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -16093,12 +16093,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (157)</t>
+          <t>إشارة إلى المادة (93)</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -16135,12 +16135,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (158)</t>
+          <t>إشارة إلى المادة (157)</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>157</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -16177,12 +16177,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (165)</t>
+          <t>إشارة إلى المادة (158)</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -16219,13 +16219,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr"/>
+          <t>إشارة إلى المادة (165)</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -16240,7 +16244,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -16257,7 +16261,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -16295,7 +16299,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -16333,17 +16337,13 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (6)</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
       <c r="C397" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -16375,13 +16375,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr"/>
+          <t>إشارة إلى المادة (6)</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -16396,7 +16400,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -16413,7 +16417,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -16451,7 +16455,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -16489,7 +16493,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -16527,7 +16531,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -16565,7 +16569,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -16603,14 +16607,10 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
       <c r="C404" t="inlineStr">
         <is>
           <t>ملف مؤقت tmp</t>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -16645,12 +16645,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -16687,12 +16687,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -16729,12 +16729,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -16771,12 +16771,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -16813,12 +16813,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -16855,17 +16855,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (176)</t>
+          <t>إشارة إلى المادة (202)</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -16907,12 +16907,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -16939,13 +16939,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr"/>
+          <t>إشارة إلى المادة (176)</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -16960,7 +16964,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -16977,7 +16981,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -17015,7 +17019,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -17053,7 +17057,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -17091,7 +17095,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -17129,7 +17133,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -17167,14 +17171,10 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
       <c r="C418" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -17209,12 +17209,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -17251,12 +17251,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -17293,12 +17293,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -17335,12 +17335,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -17377,12 +17377,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -17419,13 +17419,17 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -17440,7 +17444,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -17457,7 +17461,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -17495,7 +17499,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -17533,7 +17537,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -17571,7 +17575,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -17609,7 +17613,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -17647,14 +17651,10 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
       <c r="C430" t="inlineStr">
         <is>
           <t>شكوى لوزير العدل 13-11-1445</t>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -17689,12 +17689,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -17731,12 +17731,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -17773,12 +17773,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -17815,12 +17815,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -17857,12 +17857,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -17899,13 +17899,17 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -17920,7 +17924,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -17937,7 +17941,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -17975,13 +17979,13 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
       <c r="C438" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -18013,7 +18017,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -18051,14 +18055,10 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (175)</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
+          <t>نظام المرافعات</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
       <c r="C440" t="inlineStr">
         <is>
           <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
@@ -18076,7 +18076,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -18093,18 +18093,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr"/>
+          <t>إشارة إلى المادة (175)</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -18114,7 +18118,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -18131,7 +18135,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -18169,7 +18173,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -18207,7 +18211,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -18245,14 +18249,10 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
       <c r="C445" t="inlineStr">
         <is>
           <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
@@ -18270,7 +18270,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -18287,12 +18287,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -18329,12 +18329,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -18371,12 +18371,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -18413,12 +18413,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -18455,12 +18455,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -18497,13 +18497,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -18518,7 +18522,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -18535,7 +18539,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -18573,18 +18577,18 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -18611,7 +18615,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -18649,13 +18653,13 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -18687,7 +18691,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -18725,7 +18729,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
@@ -18763,7 +18767,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -18801,14 +18805,10 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>اللائحة التنفيذية</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
       <c r="C459" t="inlineStr">
         <is>
           <t>الشكوى الرابعة</t>
@@ -18826,7 +18826,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -18843,12 +18843,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -18885,12 +18885,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -18927,12 +18927,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -18969,12 +18969,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -19011,12 +19011,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -19053,18 +19053,22 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -19074,7 +19078,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -19091,7 +19095,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
@@ -19129,7 +19133,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -19167,7 +19171,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -19205,7 +19209,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
@@ -19243,14 +19247,10 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
       <c r="C470" t="inlineStr">
         <is>
           <t>الشكوى ومرفقاتها</t>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
@@ -19285,12 +19285,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (8)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -19327,12 +19327,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (100)</t>
+          <t>إشارة إلى المادة (8)</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -19369,12 +19369,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (100)</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -19411,13 +19411,17 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -19432,7 +19436,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -19449,7 +19453,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
@@ -19487,13 +19491,13 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>نظام المرافعات الشرعية</t>
+          <t>نظام الإثبات</t>
         </is>
       </c>
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -19525,7 +19529,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>نظام المحاكم التجارية</t>
+          <t>نظام المرافعات الشرعية</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -19563,7 +19567,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>نظام المرافعات</t>
+          <t>نظام المحاكم التجارية</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
@@ -19601,7 +19605,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>اللائحة التنفيذية</t>
+          <t>نظام المرافعات</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -19639,7 +19643,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>نظام التنفيذ</t>
+          <t>اللائحة التنفيذية</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -19677,14 +19681,10 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (1)</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>نظام التنفيذ</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr"/>
       <c r="C481" t="inlineStr">
         <is>
           <t>مرفقات الشكوى</t>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
@@ -19719,12 +19719,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (58)</t>
+          <t>إشارة إلى المادة (1)</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -19761,12 +19761,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (86)</t>
+          <t>إشارة إلى المادة (58)</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -19803,12 +19803,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (200)</t>
+          <t>إشارة إلى المادة (86)</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -19845,12 +19845,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (201)</t>
+          <t>إشارة إلى المادة (200)</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -19887,12 +19887,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>إشارة إلى المادة (202)</t>
+          <t>إشارة إلى المادة (201)</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -19929,13 +19929,17 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>نظام الاثبات</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr"/>
+          <t>إشارة إلى المادة (202)</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد.docx</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -19950,7 +19954,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -19967,7 +19971,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>نظام الإثبات</t>
+          <t>نظام الاثبات</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -19997,6 +20001,44 @@
         </is>
       </c>
       <c r="H488" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>نظام الإثبات</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr"/>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>ملخص الشكوى لولي العهد.docx</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
+++ b/zaini_case_audit_output/outputs/excel/05_official_law_verification_needed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H515"/>
+  <dimension ref="A1:H517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -21120,6 +21120,78 @@
         </is>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>إشارة إلى المادة (801)</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr"/>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>وزارة العدل / ناجز / هيئة الخبراء</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>نظام القضاء</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>يحتاج تحقق رسمي</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>هيئة الخبراء بمجلس الوزراء / جريدة أم القرى</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
